--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E64C5CB-F092-9D40-916A-66C66D3CBADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5665FBE-F189-9F4D-952F-0A93128EE00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MinigameReward" sheetId="1" r:id="rId1"/>
+    <sheet name="MinigameInfo" sheetId="2" r:id="rId1"/>
+    <sheet name="MinigameReward" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -206,6 +207,14 @@
   </si>
   <si>
     <t>[파우더_가루]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;MinigameType&gt;;key</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DurationHours</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -550,6 +559,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5665FBE-F189-9F4D-952F-0A93128EE00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F01241-5485-AF45-9775-48832A9A5612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MinigameInfo" sheetId="2" r:id="rId1"/>
@@ -38,10 +38,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>RewardIds</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -215,6 +211,10 @@
   </si>
   <si>
     <t>DurationHours</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -569,7 +569,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -620,16 +620,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
@@ -637,13 +637,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
@@ -654,7 +654,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="8">
         <v>1</v>
@@ -668,7 +668,7 @@
         <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="8">
         <v>1</v>
@@ -682,7 +682,7 @@
         <v>76</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="8">
         <v>1</v>
@@ -696,7 +696,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="8">
         <v>1</v>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F01241-5485-AF45-9775-48832A9A5612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68DF55D-10DB-294A-A8DE-69AE23371BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,7 +214,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>list&lt;int&gt;</t>
+    <t>list&lt;int&gt;d</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68DF55D-10DB-294A-A8DE-69AE23371BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC51EA31-8CDF-764E-875F-81549B4C19F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -214,7 +214,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>list&lt;int&gt;d</t>
+    <t>list&lt;int&gt;</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC51EA31-8CDF-764E-875F-81549B4C19F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6946FF-A0E4-264A-BF11-0ACD164B06EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -215,6 +215,10 @@
   </si>
   <si>
     <t>list&lt;int&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CottonCandy</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -596,6 +600,14 @@
         <v>1</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>2</v>
       </c>
     </row>
@@ -716,6 +728,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+    </row>
     <row r="11" spans="1:5" ht="13">
       <c r="E11" s="1"/>
     </row>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6946FF-A0E4-264A-BF11-0ACD164B06EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C40F782-6894-074A-BD32-F920475DFCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -219,6 +219,10 @@
   </si>
   <si>
     <t>CottonCandy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[꿈뭉치]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -736,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C40F782-6894-074A-BD32-F920475DFCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8373053D-35BF-0045-8D65-78E8FE61AA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MinigameInfo" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -223,6 +223,10 @@
   </si>
   <si>
     <t>[꿈뭉치]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinigameSeconds</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -568,51 +572,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B5">
         <v>2</v>
+      </c>
+      <c r="C5">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8373053D-35BF-0045-8D65-78E8FE61AA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9631169-9E77-DD45-8EC5-D337774BA203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -227,6 +227,26 @@
   </si>
   <si>
     <t>MinigameSeconds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum&lt;ArtifactType&gt;</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquippedArtifactType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stick</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bubblegun</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Powder</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -572,14 +592,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -589,8 +611,11 @@
       <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -600,8 +625,11 @@
       <c r="C2" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -611,8 +639,11 @@
       <c r="C3">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -622,8 +653,11 @@
       <c r="C4">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -632,6 +666,9 @@
       </c>
       <c r="C5">
         <v>60</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9631169-9E77-DD45-8EC5-D337774BA203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74399C49-83DC-F64F-A9A9-065F6BCDFD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -247,6 +247,1079 @@
   </si>
   <si>
     <t>Powder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>습기에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>약해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수분관리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수분관리를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해줘야</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하거든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마들은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>천계나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포탈로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>알지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아직</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>준비가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>애들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보이면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파우더룸으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보내줘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Title</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>방을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>너무</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>오래</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>비워두었나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>끈적끈적한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>슬라임들이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>등장해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>방을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>어지럽히기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시작했어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>걱정마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버블건과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>함께라면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>한방에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>슥삭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>버릇없는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>젤리들에게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>건법으로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>예의를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>가르쳐주자</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!</t>
+    </r>
+  </si>
+  <si>
+    <t>캐치캐치 슬라임!!</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>대신</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>포탈로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전송</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>부탁해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!</t>
+    </r>
+  </si>
+  <si>
+    <t>솜사탕</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>솜사탕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미니게임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>설명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (MinigameData)</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -257,7 +1330,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -309,6 +1382,22 @@
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -364,7 +1453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -377,6 +1466,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -592,16 +1685,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -614,8 +1708,14 @@
       <c r="D1" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="E1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -628,8 +1728,14 @@
       <c r="D2" s="8" t="s">
         <v>20</v>
       </c>
+      <c r="E2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -642,8 +1748,14 @@
       <c r="D3" s="8" t="s">
         <v>22</v>
       </c>
+      <c r="E3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -656,8 +1768,14 @@
       <c r="D4" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="E4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -669,6 +1787,12 @@
       </c>
       <c r="D5" s="8" t="s">
         <v>21</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
